--- a/resources/variable_schema_data_individual_maternalhealth_template.xlsx
+++ b/resources/variable_schema_data_individual_maternalhealth_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9670C9E2-7128-4A18-A5B7-FFADFA6DFC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1403C2-1A81-4FA1-92AE-6CE1DAB585E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14280" yWindow="0" windowWidth="14625" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="259">
   <si>
     <t>rule_type</t>
   </si>
@@ -632,6 +632,171 @@
   </si>
   <si>
     <t>المنطقة الإدارية 4</t>
+  </si>
+  <si>
+    <t>age_cat</t>
+  </si>
+  <si>
+    <t>0-4y</t>
+  </si>
+  <si>
+    <t>factor</t>
+  </si>
+  <si>
+    <t>0-4y,0-4</t>
+  </si>
+  <si>
+    <t>Age Category</t>
+  </si>
+  <si>
+    <t>Catégorie d'âge</t>
+  </si>
+  <si>
+    <t>فئة العمر</t>
+  </si>
+  <si>
+    <t>5-9y</t>
+  </si>
+  <si>
+    <t>5-9y,5-9</t>
+  </si>
+  <si>
+    <t>10-14y</t>
+  </si>
+  <si>
+    <t>10-14y,10-14</t>
+  </si>
+  <si>
+    <t>15-19y</t>
+  </si>
+  <si>
+    <t>15-19y,15-19</t>
+  </si>
+  <si>
+    <t>20-24y</t>
+  </si>
+  <si>
+    <t>20-24y,20-24</t>
+  </si>
+  <si>
+    <t>25-29y</t>
+  </si>
+  <si>
+    <t>25-29y,25-29</t>
+  </si>
+  <si>
+    <t>30-34y</t>
+  </si>
+  <si>
+    <t>30-34y,30-34</t>
+  </si>
+  <si>
+    <t>35-39y</t>
+  </si>
+  <si>
+    <t>35-39y,35-39</t>
+  </si>
+  <si>
+    <t>40-44y</t>
+  </si>
+  <si>
+    <t>40-44y,40-44</t>
+  </si>
+  <si>
+    <t>45-49y</t>
+  </si>
+  <si>
+    <t>45-49y,45-49</t>
+  </si>
+  <si>
+    <t>50-54y</t>
+  </si>
+  <si>
+    <t>50-54y,50-54</t>
+  </si>
+  <si>
+    <t>55-59y</t>
+  </si>
+  <si>
+    <t>55-59y,55-59</t>
+  </si>
+  <si>
+    <t>60-64y</t>
+  </si>
+  <si>
+    <t>60-64y,60-64</t>
+  </si>
+  <si>
+    <t>65-69y</t>
+  </si>
+  <si>
+    <t>65-69y,65-69</t>
+  </si>
+  <si>
+    <t>70-74y</t>
+  </si>
+  <si>
+    <t>70-74y,70-74</t>
+  </si>
+  <si>
+    <t>75-79y</t>
+  </si>
+  <si>
+    <t>75-79y,75-79</t>
+  </si>
+  <si>
+    <t>80-84y</t>
+  </si>
+  <si>
+    <t>80-84y,80-84</t>
+  </si>
+  <si>
+    <t>85-89y</t>
+  </si>
+  <si>
+    <t>85-89y,85-89</t>
+  </si>
+  <si>
+    <t>90-94y</t>
+  </si>
+  <si>
+    <t>90-94y,90-94</t>
+  </si>
+  <si>
+    <t>95-99y</t>
+  </si>
+  <si>
+    <t>95-99y,95-99</t>
+  </si>
+  <si>
+    <t>100-104y</t>
+  </si>
+  <si>
+    <t>100-104y,100-104</t>
+  </si>
+  <si>
+    <t>105-109y</t>
+  </si>
+  <si>
+    <t>105-109y,105-109</t>
+  </si>
+  <si>
+    <t>110-114y</t>
+  </si>
+  <si>
+    <t>110-114y,110-114</t>
+  </si>
+  <si>
+    <t>115-119y</t>
+  </si>
+  <si>
+    <t>115-119y,115-119</t>
+  </si>
+  <si>
+    <t>120-124y</t>
+  </si>
+  <si>
+    <t>120-124y,120-124</t>
   </si>
 </sst>
 </file>
@@ -673,7 +838,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="55">
+  <dxfs count="57">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1522,7 +1707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:S63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.140625" customWidth="1"/>
@@ -2897,171 +3082,1202 @@
         <v>120</v>
       </c>
     </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" t="s">
+        <v>204</v>
+      </c>
+      <c r="C39" t="s">
+        <v>205</v>
+      </c>
+      <c r="E39" t="s">
+        <v>206</v>
+      </c>
+      <c r="F39" t="s">
+        <v>109</v>
+      </c>
+      <c r="I39" t="s">
+        <v>207</v>
+      </c>
+      <c r="J39" t="s">
+        <v>204</v>
+      </c>
+      <c r="L39" t="s">
+        <v>208</v>
+      </c>
+      <c r="M39" t="s">
+        <v>209</v>
+      </c>
+      <c r="N39" t="s">
+        <v>210</v>
+      </c>
+      <c r="O39" t="s">
+        <v>205</v>
+      </c>
+      <c r="P39" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B40" t="s">
+        <v>204</v>
+      </c>
+      <c r="C40" t="s">
+        <v>211</v>
+      </c>
+      <c r="E40" t="s">
+        <v>206</v>
+      </c>
+      <c r="F40" t="s">
+        <v>109</v>
+      </c>
+      <c r="I40" t="s">
+        <v>212</v>
+      </c>
+      <c r="J40" t="s">
+        <v>204</v>
+      </c>
+      <c r="L40" t="s">
+        <v>208</v>
+      </c>
+      <c r="M40" t="s">
+        <v>209</v>
+      </c>
+      <c r="N40" t="s">
+        <v>210</v>
+      </c>
+      <c r="O40" t="s">
+        <v>211</v>
+      </c>
+      <c r="P40" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" t="s">
+        <v>204</v>
+      </c>
+      <c r="C41" t="s">
+        <v>213</v>
+      </c>
+      <c r="E41" t="s">
+        <v>206</v>
+      </c>
+      <c r="F41" t="s">
+        <v>109</v>
+      </c>
+      <c r="I41" t="s">
+        <v>214</v>
+      </c>
+      <c r="J41" t="s">
+        <v>204</v>
+      </c>
+      <c r="L41" t="s">
+        <v>208</v>
+      </c>
+      <c r="M41" t="s">
+        <v>209</v>
+      </c>
+      <c r="N41" t="s">
+        <v>210</v>
+      </c>
+      <c r="O41" t="s">
+        <v>213</v>
+      </c>
+      <c r="P41" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B42" t="s">
+        <v>204</v>
+      </c>
+      <c r="C42" t="s">
+        <v>215</v>
+      </c>
+      <c r="E42" t="s">
+        <v>206</v>
+      </c>
+      <c r="F42" t="s">
+        <v>109</v>
+      </c>
+      <c r="I42" t="s">
+        <v>216</v>
+      </c>
+      <c r="J42" t="s">
+        <v>204</v>
+      </c>
+      <c r="L42" t="s">
+        <v>208</v>
+      </c>
+      <c r="M42" t="s">
+        <v>209</v>
+      </c>
+      <c r="N42" t="s">
+        <v>210</v>
+      </c>
+      <c r="O42" t="s">
+        <v>215</v>
+      </c>
+      <c r="P42" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1</v>
+      </c>
+      <c r="B43" t="s">
+        <v>204</v>
+      </c>
+      <c r="C43" t="s">
+        <v>217</v>
+      </c>
+      <c r="E43" t="s">
+        <v>206</v>
+      </c>
+      <c r="F43" t="s">
+        <v>109</v>
+      </c>
+      <c r="I43" t="s">
+        <v>218</v>
+      </c>
+      <c r="J43" t="s">
+        <v>204</v>
+      </c>
+      <c r="L43" t="s">
+        <v>208</v>
+      </c>
+      <c r="M43" t="s">
+        <v>209</v>
+      </c>
+      <c r="N43" t="s">
+        <v>210</v>
+      </c>
+      <c r="O43" t="s">
+        <v>217</v>
+      </c>
+      <c r="P43" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1</v>
+      </c>
+      <c r="B44" t="s">
+        <v>204</v>
+      </c>
+      <c r="C44" t="s">
+        <v>219</v>
+      </c>
+      <c r="E44" t="s">
+        <v>206</v>
+      </c>
+      <c r="F44" t="s">
+        <v>109</v>
+      </c>
+      <c r="I44" t="s">
+        <v>220</v>
+      </c>
+      <c r="J44" t="s">
+        <v>204</v>
+      </c>
+      <c r="L44" t="s">
+        <v>208</v>
+      </c>
+      <c r="M44" t="s">
+        <v>209</v>
+      </c>
+      <c r="N44" t="s">
+        <v>210</v>
+      </c>
+      <c r="O44" t="s">
+        <v>219</v>
+      </c>
+      <c r="P44" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1</v>
+      </c>
+      <c r="B45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C45" t="s">
+        <v>221</v>
+      </c>
+      <c r="E45" t="s">
+        <v>206</v>
+      </c>
+      <c r="F45" t="s">
+        <v>109</v>
+      </c>
+      <c r="I45" t="s">
+        <v>222</v>
+      </c>
+      <c r="J45" t="s">
+        <v>204</v>
+      </c>
+      <c r="L45" t="s">
+        <v>208</v>
+      </c>
+      <c r="M45" t="s">
+        <v>209</v>
+      </c>
+      <c r="N45" t="s">
+        <v>210</v>
+      </c>
+      <c r="O45" t="s">
+        <v>221</v>
+      </c>
+      <c r="P45" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B46" t="s">
+        <v>204</v>
+      </c>
+      <c r="C46" t="s">
+        <v>223</v>
+      </c>
+      <c r="E46" t="s">
+        <v>206</v>
+      </c>
+      <c r="F46" t="s">
+        <v>109</v>
+      </c>
+      <c r="I46" t="s">
+        <v>224</v>
+      </c>
+      <c r="J46" t="s">
+        <v>204</v>
+      </c>
+      <c r="L46" t="s">
+        <v>208</v>
+      </c>
+      <c r="M46" t="s">
+        <v>209</v>
+      </c>
+      <c r="N46" t="s">
+        <v>210</v>
+      </c>
+      <c r="O46" t="s">
+        <v>223</v>
+      </c>
+      <c r="P46" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B47" t="s">
+        <v>204</v>
+      </c>
+      <c r="C47" t="s">
+        <v>225</v>
+      </c>
+      <c r="E47" t="s">
+        <v>206</v>
+      </c>
+      <c r="F47" t="s">
+        <v>109</v>
+      </c>
+      <c r="I47" t="s">
+        <v>226</v>
+      </c>
+      <c r="J47" t="s">
+        <v>204</v>
+      </c>
+      <c r="L47" t="s">
+        <v>208</v>
+      </c>
+      <c r="M47" t="s">
+        <v>209</v>
+      </c>
+      <c r="N47" t="s">
+        <v>210</v>
+      </c>
+      <c r="O47" t="s">
+        <v>225</v>
+      </c>
+      <c r="P47" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" t="s">
+        <v>204</v>
+      </c>
+      <c r="C48" t="s">
+        <v>227</v>
+      </c>
+      <c r="E48" t="s">
+        <v>206</v>
+      </c>
+      <c r="F48" t="s">
+        <v>109</v>
+      </c>
+      <c r="I48" t="s">
+        <v>228</v>
+      </c>
+      <c r="J48" t="s">
+        <v>204</v>
+      </c>
+      <c r="L48" t="s">
+        <v>208</v>
+      </c>
+      <c r="M48" t="s">
+        <v>209</v>
+      </c>
+      <c r="N48" t="s">
+        <v>210</v>
+      </c>
+      <c r="O48" t="s">
+        <v>227</v>
+      </c>
+      <c r="P48" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1</v>
+      </c>
+      <c r="B49" t="s">
+        <v>204</v>
+      </c>
+      <c r="C49" t="s">
+        <v>229</v>
+      </c>
+      <c r="E49" t="s">
+        <v>206</v>
+      </c>
+      <c r="F49" t="s">
+        <v>109</v>
+      </c>
+      <c r="I49" t="s">
+        <v>230</v>
+      </c>
+      <c r="J49" t="s">
+        <v>204</v>
+      </c>
+      <c r="L49" t="s">
+        <v>208</v>
+      </c>
+      <c r="M49" t="s">
+        <v>209</v>
+      </c>
+      <c r="N49" t="s">
+        <v>210</v>
+      </c>
+      <c r="O49" t="s">
+        <v>229</v>
+      </c>
+      <c r="P49" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>1</v>
+      </c>
+      <c r="B50" t="s">
+        <v>204</v>
+      </c>
+      <c r="C50" t="s">
+        <v>231</v>
+      </c>
+      <c r="E50" t="s">
+        <v>206</v>
+      </c>
+      <c r="F50" t="s">
+        <v>109</v>
+      </c>
+      <c r="I50" t="s">
+        <v>232</v>
+      </c>
+      <c r="J50" t="s">
+        <v>204</v>
+      </c>
+      <c r="L50" t="s">
+        <v>208</v>
+      </c>
+      <c r="M50" t="s">
+        <v>209</v>
+      </c>
+      <c r="N50" t="s">
+        <v>210</v>
+      </c>
+      <c r="O50" t="s">
+        <v>231</v>
+      </c>
+      <c r="P50" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B51" t="s">
+        <v>204</v>
+      </c>
+      <c r="C51" t="s">
+        <v>233</v>
+      </c>
+      <c r="E51" t="s">
+        <v>206</v>
+      </c>
+      <c r="F51" t="s">
+        <v>109</v>
+      </c>
+      <c r="I51" t="s">
+        <v>234</v>
+      </c>
+      <c r="J51" t="s">
+        <v>204</v>
+      </c>
+      <c r="L51" t="s">
+        <v>208</v>
+      </c>
+      <c r="M51" t="s">
+        <v>209</v>
+      </c>
+      <c r="N51" t="s">
+        <v>210</v>
+      </c>
+      <c r="O51" t="s">
+        <v>233</v>
+      </c>
+      <c r="P51" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52" t="s">
+        <v>204</v>
+      </c>
+      <c r="C52" t="s">
+        <v>235</v>
+      </c>
+      <c r="E52" t="s">
+        <v>206</v>
+      </c>
+      <c r="F52" t="s">
+        <v>109</v>
+      </c>
+      <c r="I52" t="s">
+        <v>236</v>
+      </c>
+      <c r="J52" t="s">
+        <v>204</v>
+      </c>
+      <c r="L52" t="s">
+        <v>208</v>
+      </c>
+      <c r="M52" t="s">
+        <v>209</v>
+      </c>
+      <c r="N52" t="s">
+        <v>210</v>
+      </c>
+      <c r="O52" t="s">
+        <v>235</v>
+      </c>
+      <c r="P52" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B53" t="s">
+        <v>204</v>
+      </c>
+      <c r="C53" t="s">
+        <v>237</v>
+      </c>
+      <c r="E53" t="s">
+        <v>206</v>
+      </c>
+      <c r="F53" t="s">
+        <v>109</v>
+      </c>
+      <c r="I53" t="s">
+        <v>238</v>
+      </c>
+      <c r="J53" t="s">
+        <v>204</v>
+      </c>
+      <c r="L53" t="s">
+        <v>208</v>
+      </c>
+      <c r="M53" t="s">
+        <v>209</v>
+      </c>
+      <c r="N53" t="s">
+        <v>210</v>
+      </c>
+      <c r="O53" t="s">
+        <v>237</v>
+      </c>
+      <c r="P53" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>1</v>
+      </c>
+      <c r="B54" t="s">
+        <v>204</v>
+      </c>
+      <c r="C54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E54" t="s">
+        <v>206</v>
+      </c>
+      <c r="F54" t="s">
+        <v>109</v>
+      </c>
+      <c r="I54" t="s">
+        <v>240</v>
+      </c>
+      <c r="J54" t="s">
+        <v>204</v>
+      </c>
+      <c r="L54" t="s">
+        <v>208</v>
+      </c>
+      <c r="M54" t="s">
+        <v>209</v>
+      </c>
+      <c r="N54" t="s">
+        <v>210</v>
+      </c>
+      <c r="O54" t="s">
+        <v>239</v>
+      </c>
+      <c r="P54" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>1</v>
+      </c>
+      <c r="B55" t="s">
+        <v>204</v>
+      </c>
+      <c r="C55" t="s">
+        <v>241</v>
+      </c>
+      <c r="E55" t="s">
+        <v>206</v>
+      </c>
+      <c r="F55" t="s">
+        <v>109</v>
+      </c>
+      <c r="I55" t="s">
+        <v>242</v>
+      </c>
+      <c r="J55" t="s">
+        <v>204</v>
+      </c>
+      <c r="L55" t="s">
+        <v>208</v>
+      </c>
+      <c r="M55" t="s">
+        <v>209</v>
+      </c>
+      <c r="N55" t="s">
+        <v>210</v>
+      </c>
+      <c r="O55" t="s">
+        <v>241</v>
+      </c>
+      <c r="P55" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>1</v>
+      </c>
+      <c r="B56" t="s">
+        <v>204</v>
+      </c>
+      <c r="C56" t="s">
+        <v>243</v>
+      </c>
+      <c r="E56" t="s">
+        <v>206</v>
+      </c>
+      <c r="F56" t="s">
+        <v>109</v>
+      </c>
+      <c r="I56" t="s">
+        <v>244</v>
+      </c>
+      <c r="J56" t="s">
+        <v>204</v>
+      </c>
+      <c r="L56" t="s">
+        <v>208</v>
+      </c>
+      <c r="M56" t="s">
+        <v>209</v>
+      </c>
+      <c r="N56" t="s">
+        <v>210</v>
+      </c>
+      <c r="O56" t="s">
+        <v>243</v>
+      </c>
+      <c r="P56" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>1</v>
+      </c>
+      <c r="B57" t="s">
+        <v>204</v>
+      </c>
+      <c r="C57" t="s">
+        <v>245</v>
+      </c>
+      <c r="E57" t="s">
+        <v>206</v>
+      </c>
+      <c r="F57" t="s">
+        <v>109</v>
+      </c>
+      <c r="I57" t="s">
+        <v>246</v>
+      </c>
+      <c r="J57" t="s">
+        <v>204</v>
+      </c>
+      <c r="L57" t="s">
+        <v>208</v>
+      </c>
+      <c r="M57" t="s">
+        <v>209</v>
+      </c>
+      <c r="N57" t="s">
+        <v>210</v>
+      </c>
+      <c r="O57" t="s">
+        <v>245</v>
+      </c>
+      <c r="P57" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>1</v>
+      </c>
+      <c r="B58" t="s">
+        <v>204</v>
+      </c>
+      <c r="C58" t="s">
+        <v>247</v>
+      </c>
+      <c r="E58" t="s">
+        <v>206</v>
+      </c>
+      <c r="F58" t="s">
+        <v>109</v>
+      </c>
+      <c r="I58" t="s">
+        <v>248</v>
+      </c>
+      <c r="J58" t="s">
+        <v>204</v>
+      </c>
+      <c r="L58" t="s">
+        <v>208</v>
+      </c>
+      <c r="M58" t="s">
+        <v>209</v>
+      </c>
+      <c r="N58" t="s">
+        <v>210</v>
+      </c>
+      <c r="O58" t="s">
+        <v>247</v>
+      </c>
+      <c r="P58" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59" t="s">
+        <v>204</v>
+      </c>
+      <c r="C59" t="s">
+        <v>249</v>
+      </c>
+      <c r="E59" t="s">
+        <v>206</v>
+      </c>
+      <c r="F59" t="s">
+        <v>109</v>
+      </c>
+      <c r="I59" t="s">
+        <v>250</v>
+      </c>
+      <c r="J59" t="s">
+        <v>204</v>
+      </c>
+      <c r="L59" t="s">
+        <v>208</v>
+      </c>
+      <c r="M59" t="s">
+        <v>209</v>
+      </c>
+      <c r="N59" t="s">
+        <v>210</v>
+      </c>
+      <c r="O59" t="s">
+        <v>249</v>
+      </c>
+      <c r="P59" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>1</v>
+      </c>
+      <c r="B60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C60" t="s">
+        <v>251</v>
+      </c>
+      <c r="E60" t="s">
+        <v>206</v>
+      </c>
+      <c r="F60" t="s">
+        <v>109</v>
+      </c>
+      <c r="I60" t="s">
+        <v>252</v>
+      </c>
+      <c r="J60" t="s">
+        <v>204</v>
+      </c>
+      <c r="L60" t="s">
+        <v>208</v>
+      </c>
+      <c r="M60" t="s">
+        <v>209</v>
+      </c>
+      <c r="N60" t="s">
+        <v>210</v>
+      </c>
+      <c r="O60" t="s">
+        <v>251</v>
+      </c>
+      <c r="P60" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>1</v>
+      </c>
+      <c r="B61" t="s">
+        <v>204</v>
+      </c>
+      <c r="C61" t="s">
+        <v>253</v>
+      </c>
+      <c r="E61" t="s">
+        <v>206</v>
+      </c>
+      <c r="F61" t="s">
+        <v>109</v>
+      </c>
+      <c r="I61" t="s">
+        <v>254</v>
+      </c>
+      <c r="J61" t="s">
+        <v>204</v>
+      </c>
+      <c r="L61" t="s">
+        <v>208</v>
+      </c>
+      <c r="M61" t="s">
+        <v>209</v>
+      </c>
+      <c r="N61" t="s">
+        <v>210</v>
+      </c>
+      <c r="O61" t="s">
+        <v>253</v>
+      </c>
+      <c r="P61" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B62" t="s">
+        <v>204</v>
+      </c>
+      <c r="C62" t="s">
+        <v>255</v>
+      </c>
+      <c r="E62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F62" t="s">
+        <v>109</v>
+      </c>
+      <c r="I62" t="s">
+        <v>256</v>
+      </c>
+      <c r="J62" t="s">
+        <v>204</v>
+      </c>
+      <c r="L62" t="s">
+        <v>208</v>
+      </c>
+      <c r="M62" t="s">
+        <v>209</v>
+      </c>
+      <c r="N62" t="s">
+        <v>210</v>
+      </c>
+      <c r="O62" t="s">
+        <v>255</v>
+      </c>
+      <c r="P62" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>1</v>
+      </c>
+      <c r="B63" t="s">
+        <v>204</v>
+      </c>
+      <c r="C63" t="s">
+        <v>257</v>
+      </c>
+      <c r="E63" t="s">
+        <v>206</v>
+      </c>
+      <c r="F63" t="s">
+        <v>109</v>
+      </c>
+      <c r="I63" t="s">
+        <v>258</v>
+      </c>
+      <c r="J63" t="s">
+        <v>204</v>
+      </c>
+      <c r="L63" t="s">
+        <v>208</v>
+      </c>
+      <c r="M63" t="s">
+        <v>209</v>
+      </c>
+      <c r="N63" t="s">
+        <v>210</v>
+      </c>
+      <c r="O63" t="s">
+        <v>257</v>
+      </c>
+      <c r="P63" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>257</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B23:B26">
+    <cfRule type="duplicateValues" dxfId="56" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B28">
+    <cfRule type="duplicateValues" dxfId="55" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29">
     <cfRule type="duplicateValues" dxfId="54" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B28">
-    <cfRule type="duplicateValues" dxfId="53" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="52" priority="15"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B30:B32">
-    <cfRule type="duplicateValues" dxfId="51" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B33:B39">
-    <cfRule type="duplicateValues" dxfId="50" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33:B38">
+    <cfRule type="duplicateValues" dxfId="52" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B80:B82">
-    <cfRule type="duplicateValues" dxfId="49" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B83">
-    <cfRule type="duplicateValues" dxfId="48" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96">
+    <cfRule type="duplicateValues" dxfId="49" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B97">
+    <cfRule type="duplicateValues" dxfId="48" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B98">
     <cfRule type="duplicateValues" dxfId="47" priority="56"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B97">
+  <conditionalFormatting sqref="B99:B109">
     <cfRule type="duplicateValues" dxfId="46" priority="55"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B98">
-    <cfRule type="duplicateValues" dxfId="45" priority="54"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B99:B109">
-    <cfRule type="duplicateValues" dxfId="44" priority="53"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B110">
-    <cfRule type="duplicateValues" dxfId="43" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111:B121 B163:B211">
-    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122:B131">
-    <cfRule type="duplicateValues" dxfId="41" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B132">
-    <cfRule type="duplicateValues" dxfId="40" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133:B164">
-    <cfRule type="duplicateValues" dxfId="39" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C23:C28">
-    <cfRule type="duplicateValues" dxfId="38" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C80:C82">
-    <cfRule type="duplicateValues" dxfId="37" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C89:C93">
-    <cfRule type="duplicateValues" dxfId="36" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C99:C109">
-    <cfRule type="duplicateValues" dxfId="35" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C119:C120">
-    <cfRule type="duplicateValues" dxfId="34" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C122:C131">
-    <cfRule type="duplicateValues" dxfId="33" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H110">
-    <cfRule type="duplicateValues" dxfId="32" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H121:H131 H133:H211">
-    <cfRule type="duplicateValues" dxfId="31" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H132">
-    <cfRule type="duplicateValues" dxfId="30" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23:I26">
-    <cfRule type="duplicateValues" dxfId="29" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I90:I92">
-    <cfRule type="duplicateValues" dxfId="28" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I99:I109">
-    <cfRule type="duplicateValues" dxfId="27" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I120">
-    <cfRule type="duplicateValues" dxfId="26" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I122:I129 I131">
-    <cfRule type="duplicateValues" dxfId="25" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I130">
-    <cfRule type="duplicateValues" dxfId="24" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I136">
+    <cfRule type="duplicateValues" dxfId="25" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I140">
+    <cfRule type="duplicateValues" dxfId="24" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I144">
     <cfRule type="duplicateValues" dxfId="23" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I140">
+  <conditionalFormatting sqref="I148">
     <cfRule type="duplicateValues" dxfId="22" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I144">
+  <conditionalFormatting sqref="I152">
     <cfRule type="duplicateValues" dxfId="21" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I148">
+  <conditionalFormatting sqref="I156">
     <cfRule type="duplicateValues" dxfId="20" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I152">
+  <conditionalFormatting sqref="I160">
     <cfRule type="duplicateValues" dxfId="19" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I156">
-    <cfRule type="duplicateValues" dxfId="18" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I160">
-    <cfRule type="duplicateValues" dxfId="17" priority="22"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I164">
-    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J23:J26">
+    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J27:J28">
+    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J29">
     <cfRule type="duplicateValues" dxfId="15" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J27:J28">
-    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J29">
-    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J30:J32">
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J33:J35">
-    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J36:J38">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J96">
+    <cfRule type="duplicateValues" dxfId="11" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J97">
+    <cfRule type="duplicateValues" dxfId="10" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J98">
     <cfRule type="duplicateValues" dxfId="9" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J97">
-    <cfRule type="duplicateValues" dxfId="8" priority="46"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J98">
-    <cfRule type="duplicateValues" dxfId="7" priority="45"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J99:J109">
-    <cfRule type="duplicateValues" dxfId="6" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J111:J120">
-    <cfRule type="duplicateValues" dxfId="5" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J121 J165:J211">
-    <cfRule type="duplicateValues" dxfId="4" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J122:J131">
-    <cfRule type="duplicateValues" dxfId="3" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J132">
-    <cfRule type="duplicateValues" dxfId="2" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J133:J164">
-    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J163:J164">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C39 C41">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I39 I41">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
